--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F383"/>
+  <dimension ref="A1:F386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9622,6 +9622,78 @@
       <c r="F383" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="C384" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="D384" t="n">
+        <v>331.41</v>
+      </c>
+      <c r="E384" t="n">
+        <v>362.44</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>321.06</v>
+      </c>
+      <c r="C385" t="n">
+        <v>327.04</v>
+      </c>
+      <c r="D385" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="E385" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>323.21</v>
+      </c>
+      <c r="C386" t="n">
+        <v>327.82</v>
+      </c>
+      <c r="D386" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="E386" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13659,6 +13731,36 @@
       </c>
       <c r="B402" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -13827,28 +13929,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01592807594598961</v>
+        <v>-0.03057458656809164</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002204752198299298</v>
+        <v>0.000818293906322598</v>
       </c>
       <c r="M2" t="n">
-        <v>5.885039891482616</v>
+        <v>5.898287766130745</v>
       </c>
       <c r="N2" t="n">
-        <v>61.49488710570705</v>
+        <v>61.65034909859881</v>
       </c>
       <c r="O2" t="n">
-        <v>7.841867577669688</v>
+        <v>7.851773627569685</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6503175121414</v>
+        <v>331.8114308810593</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13905,28 +14007,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06661385254100904</v>
+        <v>-0.06355860676634117</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003097116064452066</v>
+        <v>0.002870989224955656</v>
       </c>
       <c r="M3" t="n">
-        <v>7.335650985857909</v>
+        <v>7.289909580901539</v>
       </c>
       <c r="N3" t="n">
-        <v>76.34707327307522</v>
+        <v>75.77879999500293</v>
       </c>
       <c r="O3" t="n">
-        <v>8.737681229770015</v>
+        <v>8.705101952016584</v>
       </c>
       <c r="P3" t="n">
-        <v>327.3113477564157</v>
+        <v>327.2777362222633</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13983,28 +14085,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1663183926707062</v>
+        <v>-0.1605124658146098</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0339634182388886</v>
+        <v>0.03219432383743359</v>
       </c>
       <c r="M4" t="n">
-        <v>5.074305905082141</v>
+        <v>5.061457872630537</v>
       </c>
       <c r="N4" t="n">
-        <v>42.05626077027024</v>
+        <v>41.83170696162477</v>
       </c>
       <c r="O4" t="n">
-        <v>6.4850798584343</v>
+        <v>6.467743575747632</v>
       </c>
       <c r="P4" t="n">
-        <v>331.1572872165076</v>
+        <v>331.0934277716214</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14061,28 +14163,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04942824467726014</v>
+        <v>-0.04296878528394761</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002132204062068377</v>
+        <v>0.001638276996476118</v>
       </c>
       <c r="M5" t="n">
-        <v>5.927735632117752</v>
+        <v>5.900942372011873</v>
       </c>
       <c r="N5" t="n">
-        <v>61.69901701815756</v>
+        <v>61.34419493683045</v>
       </c>
       <c r="O5" t="n">
-        <v>7.854872183438605</v>
+        <v>7.832253503100525</v>
       </c>
       <c r="P5" t="n">
-        <v>359.570106595749</v>
+        <v>359.4994990327039</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14120,7 +14222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F383"/>
+  <dimension ref="A1:F386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26367,6 +26469,102 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-36.76403644755768,175.7505021891601</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-36.7647381859992,175.75023109654924</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-36.765481939816304,175.75002411280767</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-36.76622642401152,175.7503643436729</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-36.764033274749,175.75049123328418</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-36.7647372885382,175.75022745692516</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-36.7654801652079,175.75000531998217</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-36.76622638241466,175.75036781418777</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-36.76403983391961,175.75051388245166</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-36.76473934741916,175.7502358066511</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-36.7654801442066,175.7500050975819</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-36.76622653001596,175.75035549945764</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F386"/>
+  <dimension ref="A1:F387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9692,6 +9692,30 @@
         <v>361.65</v>
       </c>
       <c r="F386" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="C387" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="D387" t="n">
+        <v>330.72</v>
+      </c>
+      <c r="E387" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="F387" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9708,7 +9732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13760,6 +13784,16 @@
         </is>
       </c>
       <c r="B405" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -13929,28 +13963,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03057458656809164</v>
+        <v>-0.03306296458959935</v>
       </c>
       <c r="J2" t="n">
+        <v>386</v>
+      </c>
+      <c r="K2" t="n">
         <v>385</v>
       </c>
-      <c r="K2" t="n">
-        <v>384</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.000818293906322598</v>
+        <v>0.000961672879129738</v>
       </c>
       <c r="M2" t="n">
-        <v>5.898287766130745</v>
+        <v>5.89356980633774</v>
       </c>
       <c r="N2" t="n">
-        <v>61.65034909859881</v>
+        <v>61.54587111161565</v>
       </c>
       <c r="O2" t="n">
-        <v>7.851773627569685</v>
+        <v>7.845117660788501</v>
       </c>
       <c r="P2" t="n">
-        <v>331.8114308810593</v>
+        <v>331.8388751568499</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14007,28 +14041,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06355860676634117</v>
+        <v>-0.06180924574828431</v>
       </c>
       <c r="J3" t="n">
+        <v>386</v>
+      </c>
+      <c r="K3" t="n">
         <v>385</v>
       </c>
-      <c r="K3" t="n">
-        <v>384</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.002870989224955656</v>
+        <v>0.002730886057549786</v>
       </c>
       <c r="M3" t="n">
-        <v>7.289909580901539</v>
+        <v>7.27756488835393</v>
       </c>
       <c r="N3" t="n">
-        <v>75.77879999500293</v>
+        <v>75.60947703597995</v>
       </c>
       <c r="O3" t="n">
-        <v>8.705101952016584</v>
+        <v>8.695371011979876</v>
       </c>
       <c r="P3" t="n">
-        <v>327.2777362222633</v>
+        <v>327.258442551518</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14085,28 +14119,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1605124658146098</v>
+        <v>-0.1583906666068326</v>
       </c>
       <c r="J4" t="n">
+        <v>386</v>
+      </c>
+      <c r="K4" t="n">
         <v>385</v>
       </c>
-      <c r="K4" t="n">
-        <v>384</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03219432383743359</v>
+        <v>0.03152893633220999</v>
       </c>
       <c r="M4" t="n">
-        <v>5.061457872630537</v>
+        <v>5.058023948102628</v>
       </c>
       <c r="N4" t="n">
-        <v>41.83170696162477</v>
+        <v>41.763516616494</v>
       </c>
       <c r="O4" t="n">
-        <v>6.467743575747632</v>
+        <v>6.462469854203887</v>
       </c>
       <c r="P4" t="n">
-        <v>331.0934277716214</v>
+        <v>331.070026486878</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14163,28 +14197,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04296878528394761</v>
+        <v>-0.04010805437491205</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001638276996476118</v>
+        <v>0.001434506747193143</v>
       </c>
       <c r="M5" t="n">
-        <v>5.900942372011873</v>
+        <v>5.894476449773557</v>
       </c>
       <c r="N5" t="n">
-        <v>61.34419493683045</v>
+        <v>61.25986765110453</v>
       </c>
       <c r="O5" t="n">
-        <v>7.832253503100525</v>
+        <v>7.826868316964616</v>
       </c>
       <c r="P5" t="n">
-        <v>359.4994990327039</v>
+        <v>359.4681453265533</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14222,7 +14256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F386"/>
+  <dimension ref="A1:F387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26565,6 +26599,38 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-36.764049382843695,175.7505468554322</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-36.76474201340514,175.75024661847624</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-36.7654812152724,175.75001643999718</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-36.76622625091424,175.75037878549267</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
